--- a/data/trans_dic/P79$alquiler_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79$alquiler_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,48</t>
+          <t>0,9; 4,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,61</t>
+          <t>0,18; 1,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,13</t>
+          <t>0,73; 2,38</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,88</t>
+          <t>0,49; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,21</t>
+          <t>0,37; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,2</t>
+          <t>0,61; 2,17</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,72</t>
+          <t>0,67; 3,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,17</t>
+          <t>0,4; 3,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,58</t>
+          <t>0,78; 2,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,02</t>
+          <t>1,4; 3,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,95</t>
+          <t>1,18; 3,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,15</t>
+          <t>1,52; 2,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,57</t>
+          <t>1,21; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,27</t>
+          <t>2,65; 5,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,68</t>
+          <t>2,4; 4,5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,36</t>
+          <t>1,93; 5,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,18</t>
+          <t>1,66; 4,15</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,91</t>
+          <t>1,42; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,46</t>
+          <t>1,83; 2,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,04</t>
+          <t>1,78; 2,54</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>13998</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3324; 17405</t>
+          <t>4890; 22461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>317; 7079</t>
+          <t>887; 7732</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5192; 20068</t>
+          <t>7507; 24402</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3006; 12863</t>
+          <t>2346; 14773</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1412; 8377</t>
+          <t>1559; 9724</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5242; 18182</t>
+          <t>5461; 19409</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>9907</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>884; 11283</t>
+          <t>3095; 14623</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325; 3585</t>
+          <t>737; 6516</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1637; 12970</t>
+          <t>5016; 16588</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>41242</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10465; 30683</t>
+          <t>15559; 37808</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4898; 18524</t>
+          <t>9723; 25160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18406; 42241</t>
+          <t>29409; 56920</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>42412</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4027; 16195</t>
+          <t>6452; 21416</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15620; 39124</t>
+          <t>21110; 45302</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22214; 44075</t>
+          <t>31882; 59915</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>26054</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 979</t>
+          <t>0; 8004</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12362; 38489</t>
+          <t>15391; 40314</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11486; 38971</t>
+          <t>16788; 41882</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>144688</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32891; 62729</t>
+          <t>47258; 81674</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46272; 83400</t>
+          <t>64228; 100246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86343; 136352</t>
+          <t>121722; 173672</t>
         </is>
       </c>
     </row>
